--- a/output/yearly_benthic_cover_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_46_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.48061748936283</v>
+        <v>45.35382576504308</v>
       </c>
       <c r="M2" t="n">
-        <v>99.39876960690194</v>
+        <v>100.6353856901223</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99588766456873</v>
+        <v>88.11773237214278</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88280395786848</v>
+        <v>45.96488133843587</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22868479415354</v>
+        <v>2.228934928111395</v>
       </c>
       <c r="E3" t="n">
-        <v>5.67854570765151</v>
+        <v>5.731986763298952</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428949313845135</v>
+        <v>0.7429783093704652</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95750268932267</v>
+        <v>33.98473728327559</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17316684368762</v>
+        <v>34.17700223104139</v>
       </c>
       <c r="I3" t="n">
-        <v>6.571999377215664</v>
+        <v>6.608478423479585</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643093321153209</v>
+        <v>4.643614433565407</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00411233543127</v>
+        <v>11.8822676278572</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87717778067766</v>
+        <v>48.91566229068413</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640940739774</v>
+        <v>106.7628112569772</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.04326067843853</v>
+        <v>87.34136290261794</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56777882766198</v>
+        <v>42.83011204001482</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182548791026777</v>
+        <v>2.192287334934951</v>
       </c>
       <c r="E4" t="n">
-        <v>6.475690215284983</v>
+        <v>6.557520222405434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444562770338227</v>
+        <v>0.7445431455581847</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25454843829468</v>
+        <v>33.42596869364202</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24498874355584</v>
+        <v>34.24898469567649</v>
       </c>
       <c r="I4" t="n">
-        <v>5.488176481781021</v>
+        <v>5.518664150662209</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652851731461392</v>
+        <v>4.653394659738654</v>
       </c>
       <c r="K4" t="n">
-        <v>12.95673932156148</v>
+        <v>12.65863709738206</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29292631252055</v>
+        <v>44.32768201750645</v>
       </c>
       <c r="M4" t="n">
-        <v>99.817444461744</v>
+        <v>99.81643115490334</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.90911486274372</v>
+        <v>86.43945563520745</v>
       </c>
       <c r="C5" t="n">
-        <v>42.28534463952617</v>
+        <v>42.78489326116652</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127264681714913</v>
+        <v>2.149217933505374</v>
       </c>
       <c r="E5" t="n">
-        <v>7.075262318851879</v>
+        <v>7.196534868851066</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457796945478971</v>
+        <v>0.7458659029435346</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41220846471065</v>
+        <v>32.76928631405712</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30586594920327</v>
+        <v>34.30983153540259</v>
       </c>
       <c r="I5" t="n">
-        <v>4.581610662790752</v>
+        <v>4.607057187050676</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661123090924357</v>
+        <v>4.66166189339709</v>
       </c>
       <c r="K5" t="n">
-        <v>14.09088513725628</v>
+        <v>13.56054436479255</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47132087650142</v>
+        <v>43.50126614763365</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84755065328388</v>
+        <v>99.84670377359272</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.66052835541475</v>
+        <v>85.30371039858707</v>
       </c>
       <c r="C6" t="n">
-        <v>41.74826346677287</v>
+        <v>42.36502883649375</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066545917734923</v>
+        <v>2.094400543523261</v>
       </c>
       <c r="E6" t="n">
-        <v>7.510605113506627</v>
+        <v>7.653812370896051</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469024847386541</v>
+        <v>0.7469865425262731</v>
       </c>
       <c r="G6" t="n">
-        <v>31.48706301724689</v>
+        <v>31.93348147579049</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35751429797809</v>
+        <v>34.36138095620856</v>
       </c>
       <c r="I6" t="n">
-        <v>3.823756994592979</v>
+        <v>3.84498261885324</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668140529616588</v>
+        <v>4.668665890789206</v>
       </c>
       <c r="K6" t="n">
-        <v>15.33947164458525</v>
+        <v>14.69628960141293</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78499792578658</v>
+        <v>42.81070775134191</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8727330371447</v>
+        <v>99.87202618924859</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.15670300743818</v>
+        <v>83.95553329163216</v>
       </c>
       <c r="C7" t="n">
-        <v>40.83836854561066</v>
+        <v>41.61452918951079</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993412469001659</v>
+        <v>2.029239549384749</v>
       </c>
       <c r="E7" t="n">
-        <v>7.77656722388032</v>
+        <v>7.950392540313611</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478577181438102</v>
+        <v>0.7479380411799732</v>
       </c>
       <c r="G7" t="n">
-        <v>30.37276040767464</v>
+        <v>30.93996693259531</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40145503461527</v>
+        <v>34.40514989427876</v>
       </c>
       <c r="I7" t="n">
-        <v>3.190539415723661</v>
+        <v>3.208233576504925</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674110738398814</v>
+        <v>4.674612757374831</v>
       </c>
       <c r="K7" t="n">
-        <v>16.84329699256181</v>
+        <v>16.04446670836784</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2121189897555</v>
+        <v>42.23419902937546</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89378452792798</v>
+        <v>99.89319492725409</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.06928901558548</v>
+        <v>88.67141411531442</v>
       </c>
       <c r="C8" t="n">
-        <v>43.16745151177211</v>
+        <v>43.87078728001997</v>
       </c>
       <c r="D8" t="n">
-        <v>1.997675608251396</v>
+        <v>2.033471634833807</v>
       </c>
       <c r="E8" t="n">
-        <v>9.628257282174117</v>
+        <v>9.747085111145504</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494570969181561</v>
+        <v>0.749497905170321</v>
       </c>
       <c r="G8" t="n">
-        <v>30.8843800283571</v>
+        <v>31.43222745536472</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47502645823518</v>
+        <v>34.47690363783477</v>
       </c>
       <c r="I8" t="n">
-        <v>5.650385685911052</v>
+        <v>5.547866463650798</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684106855738476</v>
+        <v>4.684361907314505</v>
       </c>
       <c r="K8" t="n">
-        <v>11.93071098441451</v>
+        <v>11.32858588468558</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71389325443275</v>
+        <v>44.61608282937055</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81205575061938</v>
+        <v>99.8154559940761</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.1453730111846</v>
+        <v>86.64688752298756</v>
       </c>
       <c r="C9" t="n">
-        <v>42.12062980100976</v>
+        <v>42.70829252302787</v>
       </c>
       <c r="D9" t="n">
-        <v>1.910746887993479</v>
+        <v>1.941656497205355</v>
       </c>
       <c r="E9" t="n">
-        <v>9.995492557101029</v>
+        <v>10.07889545973421</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508250853048978</v>
+        <v>0.7508333134510415</v>
       </c>
       <c r="G9" t="n">
-        <v>29.54044830053557</v>
+        <v>30.01300220513446</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5379539240253</v>
+        <v>34.53833241874791</v>
       </c>
       <c r="I9" t="n">
-        <v>4.717249473068717</v>
+        <v>4.631459419645563</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692656783155611</v>
+        <v>4.692708209069008</v>
       </c>
       <c r="K9" t="n">
-        <v>13.8546269888154</v>
+        <v>13.35311247701245</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86778805223287</v>
+        <v>43.7844875981916</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84304484205802</v>
+        <v>99.84589259823193</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.10495588491726</v>
+        <v>84.45887443627807</v>
       </c>
       <c r="C10" t="n">
-        <v>40.81226924259383</v>
+        <v>41.23963264154416</v>
       </c>
       <c r="D10" t="n">
-        <v>1.819515759309648</v>
+        <v>1.84339352309579</v>
       </c>
       <c r="E10" t="n">
-        <v>10.17444047487318</v>
+        <v>10.21306426810921</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519966888708766</v>
+        <v>0.7519787621628942</v>
       </c>
       <c r="G10" t="n">
-        <v>28.13000065976285</v>
+        <v>28.49411003091199</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59184768806033</v>
+        <v>34.59102305949313</v>
       </c>
       <c r="I10" t="n">
-        <v>3.937175308597385</v>
+        <v>3.865437528986964</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699979305442978</v>
+        <v>4.699867263518088</v>
       </c>
       <c r="K10" t="n">
-        <v>15.89504411508274</v>
+        <v>15.54112556372191</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16165193473818</v>
+        <v>43.09059014418822</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86896529241476</v>
+        <v>99.87134834945431</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.84017194775677</v>
+        <v>81.99458388246209</v>
       </c>
       <c r="C11" t="n">
-        <v>39.15799954962797</v>
+        <v>39.37512235393429</v>
       </c>
       <c r="D11" t="n">
-        <v>1.719111083459561</v>
+        <v>1.7336392484163</v>
       </c>
       <c r="E11" t="n">
-        <v>10.16055525181668</v>
+        <v>10.14255632403034</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530029539438738</v>
+        <v>0.7529647820073233</v>
       </c>
       <c r="G11" t="n">
-        <v>26.57772853271195</v>
+        <v>26.79759198422369</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6381358814182</v>
+        <v>34.63637997233687</v>
       </c>
       <c r="I11" t="n">
-        <v>3.285369782257308</v>
+        <v>3.225421683901796</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706268462149212</v>
+        <v>4.706029887545769</v>
       </c>
       <c r="K11" t="n">
-        <v>18.15982805224319</v>
+        <v>18.00541611753792</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57280641733446</v>
+        <v>42.51208826383369</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89063401920563</v>
+        <v>99.8926267353059</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.62921302644351</v>
+        <v>79.56313216946212</v>
       </c>
       <c r="C12" t="n">
-        <v>37.45574025926562</v>
+        <v>37.44327585955295</v>
       </c>
       <c r="D12" t="n">
-        <v>1.622136526377657</v>
+        <v>1.626475526873762</v>
       </c>
       <c r="E12" t="n">
-        <v>10.04422618992114</v>
+        <v>9.964081420568094</v>
       </c>
       <c r="F12" t="n">
-        <v>0.75386693461989</v>
+        <v>0.7538136421097718</v>
       </c>
       <c r="G12" t="n">
-        <v>25.07848658290373</v>
+        <v>25.14111720838364</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67787899251494</v>
+        <v>34.6754275370495</v>
       </c>
       <c r="I12" t="n">
-        <v>2.740949458731848</v>
+        <v>2.690881571291292</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711668341374312</v>
+        <v>4.711335263186072</v>
       </c>
       <c r="K12" t="n">
-        <v>20.37078697355648</v>
+        <v>20.43686783053787</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0822124954485</v>
+        <v>42.03026126313414</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9087397282706</v>
+        <v>99.91040495322495</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.24761112279234</v>
+        <v>76.91211165344218</v>
       </c>
       <c r="C13" t="n">
-        <v>35.4978017549951</v>
+        <v>35.20820083348357</v>
       </c>
       <c r="D13" t="n">
-        <v>1.518495104642101</v>
+        <v>1.510556583309437</v>
       </c>
       <c r="E13" t="n">
-        <v>9.78354427705311</v>
+        <v>9.628038253273822</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546107008030969</v>
+        <v>0.7545469453663183</v>
       </c>
       <c r="G13" t="n">
-        <v>23.47617385388065</v>
+        <v>23.34930927849469</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71209223694246</v>
+        <v>34.70915948685064</v>
       </c>
       <c r="I13" t="n">
-        <v>2.286378069451561</v>
+        <v>2.244582697607787</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716316880019355</v>
+        <v>4.715918408539488</v>
       </c>
       <c r="K13" t="n">
-        <v>22.75238887720767</v>
+        <v>23.0878883465578</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67367188283246</v>
+        <v>41.62916410964498</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92386251503524</v>
+        <v>99.92525328968635</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.89135604151677</v>
+        <v>83.76255074271961</v>
       </c>
       <c r="C14" t="n">
-        <v>39.58348209817123</v>
+        <v>39.38649790689615</v>
       </c>
       <c r="D14" t="n">
-        <v>1.520309971183497</v>
+        <v>1.512380481788051</v>
       </c>
       <c r="E14" t="n">
-        <v>12.07364903348496</v>
+        <v>11.96703326916212</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555125922273633</v>
+        <v>0.755458011552718</v>
       </c>
       <c r="G14" t="n">
-        <v>25.28131966745732</v>
+        <v>25.1991827698147</v>
       </c>
       <c r="H14" t="n">
-        <v>36.53066693301796</v>
+        <v>36.572749255827</v>
       </c>
       <c r="I14" t="n">
-        <v>3.007944142724656</v>
+        <v>3.03413438237052</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72195370142102</v>
+        <v>4.721612572204486</v>
       </c>
       <c r="K14" t="n">
-        <v>16.10864395848322</v>
+        <v>16.2374492572804</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20772882946881</v>
+        <v>44.27503699311441</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89985488612325</v>
+        <v>99.89898415729097</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.19665173103766</v>
+        <v>82.86114927058836</v>
       </c>
       <c r="C15" t="n">
-        <v>39.35385697369689</v>
+        <v>38.95406061329335</v>
       </c>
       <c r="D15" t="n">
-        <v>1.494642974396199</v>
+        <v>1.478638565151402</v>
       </c>
       <c r="E15" t="n">
-        <v>12.28800277140618</v>
+        <v>12.12187977465466</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562721127343904</v>
+        <v>0.7562272015951506</v>
       </c>
       <c r="G15" t="n">
-        <v>24.85450174020388</v>
+        <v>24.63697720410578</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56739139129496</v>
+        <v>36.60998679136408</v>
       </c>
       <c r="I15" t="n">
-        <v>2.509140036412111</v>
+        <v>2.531019723747603</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726700704589939</v>
+        <v>4.726420009969689</v>
       </c>
       <c r="K15" t="n">
-        <v>16.80334826896235</v>
+        <v>17.13885072941165</v>
       </c>
       <c r="L15" t="n">
-        <v>43.7592407533762</v>
+        <v>43.82280714667358</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91644599603543</v>
+        <v>99.91571848937858</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.84232256148337</v>
+        <v>80.34380089474391</v>
       </c>
       <c r="C16" t="n">
-        <v>37.38758210091028</v>
+        <v>36.8279048868497</v>
       </c>
       <c r="D16" t="n">
-        <v>1.404779020231942</v>
+        <v>1.382502838941681</v>
       </c>
       <c r="E16" t="n">
-        <v>11.89799094777747</v>
+        <v>11.68559743693156</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569246965407648</v>
+        <v>0.7568895296524473</v>
       </c>
       <c r="G16" t="n">
-        <v>23.3601490128849</v>
+        <v>23.03517014256297</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59894522894346</v>
+        <v>36.64205099294006</v>
       </c>
       <c r="I16" t="n">
-        <v>2.092754301725067</v>
+        <v>2.111030393387394</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730779353379779</v>
+        <v>4.730559560327793</v>
       </c>
       <c r="K16" t="n">
-        <v>19.15767743851662</v>
+        <v>19.65619910525611</v>
       </c>
       <c r="L16" t="n">
-        <v>43.38504212622833</v>
+        <v>43.44558990445677</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93030166565524</v>
+        <v>99.92969389656257</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.45666921643864</v>
+        <v>81.94388275555647</v>
       </c>
       <c r="C17" t="n">
-        <v>38.56288626096192</v>
+        <v>37.9866971538789</v>
       </c>
       <c r="D17" t="n">
-        <v>1.405971118794263</v>
+        <v>1.383700441850439</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65502617157365</v>
+        <v>12.43693788397179</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575670245009178</v>
+        <v>0.7575451905862171</v>
       </c>
       <c r="G17" t="n">
-        <v>23.77704649608177</v>
+        <v>23.44141988382609</v>
       </c>
       <c r="H17" t="n">
-        <v>37.02707718368976</v>
+        <v>37.06008779143482</v>
       </c>
       <c r="I17" t="n">
-        <v>2.099187318667544</v>
+        <v>2.129534122723275</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734793903130735</v>
+        <v>4.734657441163854</v>
       </c>
       <c r="K17" t="n">
-        <v>17.54333078356134</v>
+        <v>18.05611724444353</v>
       </c>
       <c r="L17" t="n">
-        <v>43.82386937367358</v>
+        <v>43.88626256850162</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93008641819685</v>
+        <v>99.92907696682406</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.19436907668047</v>
+        <v>79.58048223721495</v>
       </c>
       <c r="C18" t="n">
-        <v>36.62486446545181</v>
+        <v>35.95197151004903</v>
       </c>
       <c r="D18" t="n">
-        <v>1.322871345183707</v>
+        <v>1.296901230379663</v>
       </c>
       <c r="E18" t="n">
-        <v>12.19881813662154</v>
+        <v>11.95276026426712</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581182658397995</v>
+        <v>0.7581087075846867</v>
       </c>
       <c r="G18" t="n">
-        <v>22.3717066889266</v>
+        <v>21.97094498902123</v>
       </c>
       <c r="H18" t="n">
-        <v>37.05401982366945</v>
+        <v>37.08765576981389</v>
       </c>
       <c r="I18" t="n">
-        <v>1.750595654940637</v>
+        <v>1.77593185374408</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738239161498746</v>
+        <v>4.73817942240429</v>
       </c>
       <c r="K18" t="n">
-        <v>19.80563092331952</v>
+        <v>20.41951776278505</v>
       </c>
       <c r="L18" t="n">
-        <v>43.51119385237678</v>
+        <v>43.56935700153473</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94168924114811</v>
+        <v>99.94084627436881</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.28496636075964</v>
+        <v>78.63999738897762</v>
       </c>
       <c r="C19" t="n">
-        <v>35.9852500060592</v>
+        <v>35.28488754492428</v>
       </c>
       <c r="D19" t="n">
-        <v>1.290146077734691</v>
+        <v>1.263062810572261</v>
       </c>
       <c r="E19" t="n">
-        <v>12.14033057203845</v>
+        <v>11.88770388697991</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585835260431576</v>
+        <v>0.7585845731860237</v>
       </c>
       <c r="G19" t="n">
-        <v>21.81827412169203</v>
+        <v>21.39768463373095</v>
       </c>
       <c r="H19" t="n">
-        <v>37.07676002341823</v>
+        <v>37.11093572879406</v>
       </c>
       <c r="I19" t="n">
-        <v>1.45972500206333</v>
+        <v>1.48087217330177</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741147037769734</v>
+        <v>4.741153582412646</v>
       </c>
       <c r="K19" t="n">
-        <v>20.71503363924038</v>
+        <v>21.36000261102236</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25108869761873</v>
+        <v>43.30577840367158</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9513723429183</v>
+        <v>99.95066855961824</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.80801690294491</v>
+        <v>76.06206536230412</v>
       </c>
       <c r="C20" t="n">
-        <v>33.73312442331353</v>
+        <v>32.93478056853196</v>
       </c>
       <c r="D20" t="n">
-        <v>1.20012034890848</v>
+        <v>1.169448200066648</v>
       </c>
       <c r="E20" t="n">
-        <v>11.49603122641341</v>
+        <v>11.21240918808523</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589842033358751</v>
+        <v>0.7589950474188621</v>
       </c>
       <c r="G20" t="n">
-        <v>20.29580619078591</v>
+        <v>19.81174932161366</v>
       </c>
       <c r="H20" t="n">
-        <v>37.09634364910862</v>
+        <v>37.13101665768669</v>
       </c>
       <c r="I20" t="n">
-        <v>1.217080013543408</v>
+        <v>1.234727901065141</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743651270849218</v>
+        <v>4.743719046367887</v>
       </c>
       <c r="K20" t="n">
-        <v>23.19198309705508</v>
+        <v>23.93793463769589</v>
       </c>
       <c r="L20" t="n">
-        <v>43.03434456290741</v>
+        <v>43.08614945562485</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95945208327602</v>
+        <v>99.9588646618527</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.41026200245894</v>
+        <v>82.06305710937501</v>
       </c>
       <c r="C21" t="n">
-        <v>37.19229949290084</v>
+        <v>36.60796582538037</v>
       </c>
       <c r="D21" t="n">
-        <v>1.200967778067099</v>
+        <v>1.17032523127584</v>
       </c>
       <c r="E21" t="n">
-        <v>13.37152143940168</v>
+        <v>13.2037292717165</v>
       </c>
       <c r="F21" t="n">
-        <v>0.75952013737401</v>
+        <v>0.7595642580467211</v>
       </c>
       <c r="G21" t="n">
-        <v>21.88655237008759</v>
+        <v>21.50180131886242</v>
       </c>
       <c r="H21" t="n">
-        <v>38.69895302641007</v>
+        <v>38.83405729177564</v>
       </c>
       <c r="I21" t="n">
-        <v>1.745746392530927</v>
+        <v>1.84630312490587</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747000858587561</v>
+        <v>4.747276612792005</v>
       </c>
       <c r="K21" t="n">
-        <v>17.58973799754108</v>
+        <v>17.93694289062501</v>
       </c>
       <c r="L21" t="n">
-        <v>45.15981202436959</v>
+        <v>45.39359396659666</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94184951481151</v>
+        <v>99.93850268260204</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_46_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.35382576504308</v>
+        <v>45.64088467356863</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6353856901223</v>
+        <v>99.03265424224367</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.11773237214278</v>
+        <v>88.07618480929909</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96488133843587</v>
+        <v>45.94404592507479</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228934928111395</v>
+        <v>2.228844284984582</v>
       </c>
       <c r="E3" t="n">
-        <v>5.731986763298952</v>
+        <v>5.717819827586959</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429783093704652</v>
+        <v>0.7429480949948606</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98473728327559</v>
+        <v>33.97793953792198</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17700223104139</v>
+        <v>34.17561236976358</v>
       </c>
       <c r="I3" t="n">
-        <v>6.608478423479585</v>
+        <v>6.589595100329244</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643614433565407</v>
+        <v>4.643425593717879</v>
       </c>
       <c r="K3" t="n">
-        <v>11.8822676278572</v>
+        <v>11.92381519070093</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91566229068413</v>
+        <v>48.89561827505575</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7628112569772</v>
+        <v>106.7634793908315</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.34136290261794</v>
+        <v>87.15298152744683</v>
       </c>
       <c r="C4" t="n">
-        <v>42.83011204001482</v>
+        <v>42.65957000534851</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192287334934951</v>
+        <v>2.184351599991618</v>
       </c>
       <c r="E4" t="n">
-        <v>6.557520222405434</v>
+        <v>6.520827231979418</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445431455581847</v>
+        <v>0.7445117665868048</v>
       </c>
       <c r="G4" t="n">
-        <v>33.42596869364202</v>
+        <v>33.29966435703324</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24898469567649</v>
+        <v>34.24754126299302</v>
       </c>
       <c r="I4" t="n">
-        <v>5.518664150662209</v>
+        <v>5.502886767695188</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653394659738654</v>
+        <v>4.653198541167531</v>
       </c>
       <c r="K4" t="n">
-        <v>12.65863709738206</v>
+        <v>12.84701847255318</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32768201750645</v>
+        <v>44.31036721375583</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81643115490334</v>
+        <v>99.81695569165753</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.43945563520745</v>
+        <v>86.07049109528285</v>
       </c>
       <c r="C5" t="n">
-        <v>42.78489326116652</v>
+        <v>42.43115435227368</v>
       </c>
       <c r="D5" t="n">
-        <v>2.149217933505374</v>
+        <v>2.131845604673544</v>
       </c>
       <c r="E5" t="n">
-        <v>7.196534868851066</v>
+        <v>7.129733504758832</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458659029435346</v>
+        <v>0.745836343975479</v>
       </c>
       <c r="G5" t="n">
-        <v>32.76928631405712</v>
+        <v>32.49922910621074</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30983153540259</v>
+        <v>34.30847182287204</v>
       </c>
       <c r="I5" t="n">
-        <v>4.607057187050676</v>
+        <v>4.593897562945471</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66166189339709</v>
+        <v>4.661477149846745</v>
       </c>
       <c r="K5" t="n">
-        <v>13.56054436479255</v>
+        <v>13.92950890471714</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50126614763365</v>
+        <v>43.48647877723988</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84670377359272</v>
+        <v>99.8471420342307</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.30371039858707</v>
+        <v>84.65339322284352</v>
       </c>
       <c r="C6" t="n">
-        <v>42.36502883649375</v>
+        <v>41.72758801536613</v>
       </c>
       <c r="D6" t="n">
-        <v>2.094400543523261</v>
+        <v>2.062613465602023</v>
       </c>
       <c r="E6" t="n">
-        <v>7.653812370896051</v>
+        <v>7.537198470806663</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469865425262731</v>
+        <v>0.7469623303517336</v>
       </c>
       <c r="G6" t="n">
-        <v>31.93348147579049</v>
+        <v>31.44380973425161</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36138095620856</v>
+        <v>34.36026719617975</v>
       </c>
       <c r="I6" t="n">
-        <v>3.84498261885324</v>
+        <v>3.834027460953413</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668665890789206</v>
+        <v>4.668514564698336</v>
       </c>
       <c r="K6" t="n">
-        <v>14.69628960141293</v>
+        <v>15.34660677715647</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81070775134191</v>
+        <v>42.79819694184001</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87202618924859</v>
+        <v>99.87239173436261</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.95553329163216</v>
+        <v>83.0317351190819</v>
       </c>
       <c r="C7" t="n">
-        <v>41.61452918951079</v>
+        <v>40.70142971127173</v>
       </c>
       <c r="D7" t="n">
-        <v>2.029239549384749</v>
+        <v>1.983662718302596</v>
       </c>
       <c r="E7" t="n">
-        <v>7.950392540313611</v>
+        <v>7.781884497862025</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479380411799732</v>
+        <v>0.7479216530306027</v>
       </c>
       <c r="G7" t="n">
-        <v>30.93996693259531</v>
+        <v>30.24023363147678</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40514989427876</v>
+        <v>34.40439603940772</v>
       </c>
       <c r="I7" t="n">
-        <v>3.208233576504925</v>
+        <v>3.199126247560918</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674612757374831</v>
+        <v>4.674510331441267</v>
       </c>
       <c r="K7" t="n">
-        <v>16.04446670836784</v>
+        <v>16.96826488091808</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23419902937546</v>
+        <v>42.22380464500593</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89319492725409</v>
+        <v>99.89349923719574</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.67141411531442</v>
+        <v>87.8303948945545</v>
       </c>
       <c r="C8" t="n">
-        <v>43.87078728001997</v>
+        <v>43.00814398949969</v>
       </c>
       <c r="D8" t="n">
-        <v>2.033471634833807</v>
+        <v>1.987855895724429</v>
       </c>
       <c r="E8" t="n">
-        <v>9.747085111145504</v>
+        <v>9.613907001975456</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749497905170321</v>
+        <v>0.7495026517355999</v>
       </c>
       <c r="G8" t="n">
-        <v>31.43222745536472</v>
+        <v>30.74779146507987</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47690363783477</v>
+        <v>34.4771219798376</v>
       </c>
       <c r="I8" t="n">
-        <v>5.547866463650798</v>
+        <v>5.569824326854042</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684361907314505</v>
+        <v>4.6843915733475</v>
       </c>
       <c r="K8" t="n">
-        <v>11.32858588468558</v>
+        <v>12.16960510544549</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61608282937055</v>
+        <v>44.63698172653205</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8154559940761</v>
+        <v>99.81473082147723</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.64688752298756</v>
+        <v>85.72016144090372</v>
       </c>
       <c r="C9" t="n">
-        <v>42.70829252302787</v>
+        <v>41.76241027292761</v>
       </c>
       <c r="D9" t="n">
-        <v>1.941656497205355</v>
+        <v>1.892218428832468</v>
       </c>
       <c r="E9" t="n">
-        <v>10.07889545973421</v>
+        <v>9.926359111483555</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508333134510415</v>
+        <v>0.7508578840917165</v>
       </c>
       <c r="G9" t="n">
-        <v>30.01300220513446</v>
+        <v>29.26848861693713</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53833241874791</v>
+        <v>34.53946266821896</v>
       </c>
       <c r="I9" t="n">
-        <v>4.631459419645563</v>
+        <v>4.649912955766655</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692708209069008</v>
+        <v>4.692861775573228</v>
       </c>
       <c r="K9" t="n">
-        <v>13.35311247701245</v>
+        <v>14.2798385590963</v>
       </c>
       <c r="L9" t="n">
-        <v>43.7844875981916</v>
+        <v>43.80303382556346</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84589259823193</v>
+        <v>99.84528265758736</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.45887443627807</v>
+        <v>83.30115365053017</v>
       </c>
       <c r="C10" t="n">
-        <v>41.23963264154416</v>
+        <v>40.06473749482782</v>
       </c>
       <c r="D10" t="n">
-        <v>1.84339352309579</v>
+        <v>1.783579321170869</v>
       </c>
       <c r="E10" t="n">
-        <v>10.21306426810921</v>
+        <v>10.00327510272557</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519787621628942</v>
+        <v>0.7520239496773818</v>
       </c>
       <c r="G10" t="n">
-        <v>28.49411003091199</v>
+        <v>27.58807876705016</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59102305949313</v>
+        <v>34.59310168515956</v>
       </c>
       <c r="I10" t="n">
-        <v>3.865437528986964</v>
+        <v>3.880945139263011</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699867263518088</v>
+        <v>4.700149685483637</v>
       </c>
       <c r="K10" t="n">
-        <v>15.54112556372191</v>
+        <v>16.69884634946983</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09059014418822</v>
+        <v>43.10725190693107</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87134834945431</v>
+        <v>99.87083575122873</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.99458388246209</v>
+        <v>80.71913607238992</v>
       </c>
       <c r="C11" t="n">
-        <v>39.37512235393429</v>
+        <v>38.08395972071466</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7336392484163</v>
+        <v>1.668849643919497</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14255632403034</v>
+        <v>9.899550180789358</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529647820073233</v>
+        <v>0.7530296546026987</v>
       </c>
       <c r="G11" t="n">
-        <v>26.79759198422369</v>
+        <v>25.81346110056407</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63637997233687</v>
+        <v>34.63936411172413</v>
       </c>
       <c r="I11" t="n">
-        <v>3.225421683901796</v>
+        <v>3.238446039523282</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706029887545769</v>
+        <v>4.706435341266867</v>
       </c>
       <c r="K11" t="n">
-        <v>18.00541611753792</v>
+        <v>19.28086392761012</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51208826383369</v>
+        <v>42.52737232002904</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8926267353059</v>
+        <v>99.8921959683538</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.56313216946212</v>
+        <v>78.05830135277893</v>
       </c>
       <c r="C12" t="n">
-        <v>37.44327585955295</v>
+        <v>35.92384003242066</v>
       </c>
       <c r="D12" t="n">
-        <v>1.626475526873762</v>
+        <v>1.551849600568616</v>
       </c>
       <c r="E12" t="n">
-        <v>9.964081420568094</v>
+        <v>9.655813659837067</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538136421097718</v>
+        <v>0.7538984708431785</v>
       </c>
       <c r="G12" t="n">
-        <v>25.14111720838364</v>
+        <v>24.00372582644494</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6754275370495</v>
+        <v>34.67932965878621</v>
       </c>
       <c r="I12" t="n">
-        <v>2.690881571291292</v>
+        <v>2.701818693529045</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711335263186072</v>
+        <v>4.711865442769867</v>
       </c>
       <c r="K12" t="n">
-        <v>20.43686783053787</v>
+        <v>21.94169864722109</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03026126313414</v>
+        <v>42.04450448592707</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91040495322495</v>
+        <v>99.91004316556881</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.91211165344218</v>
+        <v>75.43568952662267</v>
       </c>
       <c r="C13" t="n">
-        <v>35.20820083348357</v>
+        <v>33.71792832786105</v>
       </c>
       <c r="D13" t="n">
-        <v>1.510556583309437</v>
+        <v>1.43769521891181</v>
       </c>
       <c r="E13" t="n">
-        <v>9.628038253273822</v>
+        <v>9.321156289285922</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545469453663183</v>
+        <v>0.754649266914641</v>
       </c>
       <c r="G13" t="n">
-        <v>23.34930927849469</v>
+        <v>22.23800672700818</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70915948685064</v>
+        <v>34.71386627807348</v>
       </c>
       <c r="I13" t="n">
-        <v>2.244582697607787</v>
+        <v>2.253757828212136</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715918408539488</v>
+        <v>4.716557918216507</v>
       </c>
       <c r="K13" t="n">
-        <v>23.0878883465578</v>
+        <v>24.56431047337731</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62916410964498</v>
+        <v>41.64271067949694</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92525328968635</v>
+        <v>99.92494948073532</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.76255074271961</v>
+        <v>82.79682516100608</v>
       </c>
       <c r="C14" t="n">
-        <v>39.38649790689615</v>
+        <v>38.33732101259834</v>
       </c>
       <c r="D14" t="n">
-        <v>1.512380481788051</v>
+        <v>1.43936421662596</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96703326916212</v>
+        <v>11.86783944977774</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755458011552718</v>
+        <v>0.7555253273514412</v>
       </c>
       <c r="G14" t="n">
-        <v>25.1991827698147</v>
+        <v>24.31909721041301</v>
       </c>
       <c r="H14" t="n">
-        <v>36.572749255827</v>
+        <v>36.80943979014731</v>
       </c>
       <c r="I14" t="n">
-        <v>3.03413438237052</v>
+        <v>2.88352587074413</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721612572204486</v>
+        <v>4.722033295946508</v>
       </c>
       <c r="K14" t="n">
-        <v>16.2374492572804</v>
+        <v>17.2031748389939</v>
       </c>
       <c r="L14" t="n">
-        <v>44.27503699311441</v>
+        <v>44.36349807132428</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89898415729097</v>
+        <v>99.90399392291653</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.86114927058836</v>
+        <v>81.84771075044847</v>
       </c>
       <c r="C15" t="n">
-        <v>38.95406061329335</v>
+        <v>37.83320149788052</v>
       </c>
       <c r="D15" t="n">
-        <v>1.478638565151402</v>
+        <v>1.404431006234455</v>
       </c>
       <c r="E15" t="n">
-        <v>12.12187977465466</v>
+        <v>11.98069031460728</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562272015951506</v>
+        <v>0.7562654250613355</v>
       </c>
       <c r="G15" t="n">
-        <v>24.63697720410578</v>
+        <v>23.72887541000292</v>
       </c>
       <c r="H15" t="n">
-        <v>36.60998679136408</v>
+        <v>36.84549759139493</v>
       </c>
       <c r="I15" t="n">
-        <v>2.531019723747603</v>
+        <v>2.405292096514196</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726420009969689</v>
+        <v>4.726658906633348</v>
       </c>
       <c r="K15" t="n">
-        <v>17.13885072941165</v>
+        <v>18.15228924955155</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82280714667358</v>
+        <v>43.93441131171392</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91571848937858</v>
+        <v>99.91990205914598</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.34380089474391</v>
+        <v>79.16458445726488</v>
       </c>
       <c r="C16" t="n">
-        <v>36.8279048868497</v>
+        <v>35.52120420946049</v>
       </c>
       <c r="D16" t="n">
-        <v>1.382502838941681</v>
+        <v>1.303999360707169</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68559743693156</v>
+        <v>11.4582949932264</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568895296524473</v>
+        <v>0.756904240385026</v>
       </c>
       <c r="G16" t="n">
-        <v>23.03517014256297</v>
+        <v>22.03201027860129</v>
       </c>
       <c r="H16" t="n">
-        <v>36.64205099294006</v>
+        <v>36.87662088183026</v>
       </c>
       <c r="I16" t="n">
-        <v>2.111030393387394</v>
+        <v>2.006103200108315</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730559560327793</v>
+        <v>4.730651502406413</v>
       </c>
       <c r="K16" t="n">
-        <v>19.65619910525611</v>
+        <v>20.83541554273512</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44558990445677</v>
+        <v>43.57656657845678</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92969389656257</v>
+        <v>99.93318633065239</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.94388275555647</v>
+        <v>80.95861057705139</v>
       </c>
       <c r="C17" t="n">
-        <v>37.9866971538789</v>
+        <v>36.82393077149944</v>
       </c>
       <c r="D17" t="n">
-        <v>1.383700441850439</v>
+        <v>1.305068976388633</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43693788397179</v>
+        <v>12.27059401359821</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575451905862171</v>
+        <v>0.757525097012167</v>
       </c>
       <c r="G17" t="n">
-        <v>23.44141988382609</v>
+        <v>22.52094780192088</v>
       </c>
       <c r="H17" t="n">
-        <v>37.06008779143482</v>
+        <v>37.37773481317955</v>
       </c>
       <c r="I17" t="n">
-        <v>2.129534122723275</v>
+        <v>1.992208018625911</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734657441163854</v>
+        <v>4.734531856326044</v>
       </c>
       <c r="K17" t="n">
-        <v>18.05611724444353</v>
+        <v>19.04138942294859</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88626256850162</v>
+        <v>44.06832729776161</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92907696682406</v>
+        <v>99.93364749220964</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.58048223721495</v>
+        <v>78.48293739125219</v>
       </c>
       <c r="C18" t="n">
-        <v>35.95197151004903</v>
+        <v>34.65515826126319</v>
       </c>
       <c r="D18" t="n">
-        <v>1.296901230379663</v>
+        <v>1.216418995104949</v>
       </c>
       <c r="E18" t="n">
-        <v>11.95276026426712</v>
+        <v>11.71397489671893</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581087075846867</v>
+        <v>0.7580596124993745</v>
       </c>
       <c r="G18" t="n">
-        <v>21.97094498902123</v>
+        <v>20.99115770097483</v>
       </c>
       <c r="H18" t="n">
-        <v>37.08765576981389</v>
+        <v>37.40410882799857</v>
       </c>
       <c r="I18" t="n">
-        <v>1.77593185374408</v>
+        <v>1.661344779834457</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73817942240429</v>
+        <v>4.737872578121092</v>
       </c>
       <c r="K18" t="n">
-        <v>20.41951776278505</v>
+        <v>21.51706260874777</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56935700153473</v>
+        <v>43.77244001836052</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94084627436881</v>
+        <v>99.94466088837149</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.63999738897762</v>
+        <v>77.52044175948571</v>
       </c>
       <c r="C19" t="n">
-        <v>35.28488754492428</v>
+        <v>33.94278554092552</v>
       </c>
       <c r="D19" t="n">
-        <v>1.263062810572261</v>
+        <v>1.182399279231865</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88770388697991</v>
+        <v>11.61806782363499</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585845731860237</v>
+        <v>0.7585127615143851</v>
       </c>
       <c r="G19" t="n">
-        <v>21.39768463373095</v>
+        <v>20.40409582204336</v>
       </c>
       <c r="H19" t="n">
-        <v>37.11093572879406</v>
+        <v>37.42646806570663</v>
       </c>
       <c r="I19" t="n">
-        <v>1.48087217330177</v>
+        <v>1.390193247889566</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741153582412646</v>
+        <v>4.740704759464908</v>
       </c>
       <c r="K19" t="n">
-        <v>21.36000261102236</v>
+        <v>22.4795582405143</v>
       </c>
       <c r="L19" t="n">
-        <v>43.30577840367158</v>
+        <v>43.53134412783628</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95066855961824</v>
+        <v>99.9536879092761</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.06206536230412</v>
+        <v>74.84420733518594</v>
       </c>
       <c r="C20" t="n">
-        <v>32.93478056853196</v>
+        <v>31.47992365766505</v>
       </c>
       <c r="D20" t="n">
-        <v>1.169448200066648</v>
+        <v>1.087660984558522</v>
       </c>
       <c r="E20" t="n">
-        <v>11.21240918808523</v>
+        <v>10.88036643231399</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589950474188621</v>
+        <v>0.758904324389205</v>
       </c>
       <c r="G20" t="n">
-        <v>19.81174932161366</v>
+        <v>18.76924262440975</v>
       </c>
       <c r="H20" t="n">
-        <v>37.13101665768669</v>
+        <v>37.44578852565631</v>
       </c>
       <c r="I20" t="n">
-        <v>1.234727901065141</v>
+        <v>1.159092416425632</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743719046367887</v>
+        <v>4.743152027432532</v>
       </c>
       <c r="K20" t="n">
-        <v>23.93793463769589</v>
+        <v>25.15579266481406</v>
       </c>
       <c r="L20" t="n">
-        <v>43.08614945562485</v>
+        <v>43.32566719841284</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9588646618527</v>
+        <v>99.96138352089196</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.06305710937501</v>
+        <v>81.12473210608701</v>
       </c>
       <c r="C21" t="n">
-        <v>36.60796582538037</v>
+        <v>35.42762393173053</v>
       </c>
       <c r="D21" t="n">
-        <v>1.17032523127584</v>
+        <v>1.088387081020915</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2037292717165</v>
+        <v>12.99005928636666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595642580467211</v>
+        <v>0.759410950767329</v>
       </c>
       <c r="G21" t="n">
-        <v>21.50180131886242</v>
+        <v>20.61341724807757</v>
       </c>
       <c r="H21" t="n">
-        <v>38.83405729177564</v>
+        <v>39.30243116472703</v>
       </c>
       <c r="I21" t="n">
-        <v>1.84630312490587</v>
+        <v>1.624707932831712</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747276612792005</v>
+        <v>4.746318442295807</v>
       </c>
       <c r="K21" t="n">
-        <v>17.93694289062501</v>
+        <v>18.87526789391299</v>
       </c>
       <c r="L21" t="n">
-        <v>45.39359396659666</v>
+        <v>45.64298737301479</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93850268260204</v>
+        <v>99.9458791986583</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_46_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.64088467356863</v>
+        <v>43.95954155415694</v>
       </c>
       <c r="M2" t="n">
-        <v>99.03265424224367</v>
+        <v>93.79329599745014</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07618480929909</v>
+        <v>81.34034904059624</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94404592507479</v>
+        <v>43.0959045961518</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228844284984582</v>
+        <v>2.171993253699241</v>
       </c>
       <c r="E3" t="n">
-        <v>5.717819827586959</v>
+        <v>4.151072560661168</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429480949948606</v>
+        <v>0.7375364534428405</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97793953792198</v>
+        <v>32.67039852439276</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17561236976358</v>
+        <v>33.92667685837066</v>
       </c>
       <c r="I3" t="n">
-        <v>6.589595100329244</v>
+        <v>3.073068556011835</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643425593717879</v>
+        <v>4.609602834017752</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92381519070093</v>
+        <v>18.65965095940376</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89561827505575</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634793908315</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15298152744683</v>
+        <v>88.18274252091742</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65957000534851</v>
+        <v>42.60301109184162</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184351599991618</v>
+        <v>2.177603980850855</v>
       </c>
       <c r="E4" t="n">
-        <v>6.520827231979418</v>
+        <v>6.461073638069768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445117665868048</v>
+        <v>0.739441669215306</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29966435703324</v>
+        <v>33.33494457236248</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24754126299302</v>
+        <v>34.01431678390406</v>
       </c>
       <c r="I4" t="n">
-        <v>5.502886767695188</v>
+        <v>6.833851443919281</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653198541167531</v>
+        <v>4.621510432595661</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84701847255318</v>
+        <v>11.81725747908258</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31036721375583</v>
+        <v>45.3525233085375</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81695569165753</v>
+        <v>99.77279187946171</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.07049109528285</v>
+        <v>86.71388608808337</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43115435227368</v>
+        <v>42.19335346154203</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131845604673544</v>
+        <v>2.106009631942294</v>
       </c>
       <c r="E5" t="n">
-        <v>7.129733504758832</v>
+        <v>7.199877583283042</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745836343975479</v>
+        <v>0.7410639651475978</v>
       </c>
       <c r="G5" t="n">
-        <v>32.49922910621074</v>
+        <v>32.23897226814731</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30847182287204</v>
+        <v>34.08894239678948</v>
       </c>
       <c r="I5" t="n">
-        <v>4.593897562945471</v>
+        <v>5.707370460601157</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661477149846745</v>
+        <v>4.631649782172485</v>
       </c>
       <c r="K5" t="n">
-        <v>13.92950890471714</v>
+        <v>13.28611391191663</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48647877723988</v>
+        <v>44.3307034197658</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8471420342307</v>
+        <v>99.81017079322446</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.65339322284352</v>
+        <v>84.93953050096808</v>
       </c>
       <c r="C6" t="n">
-        <v>41.72758801536613</v>
+        <v>41.30425820315513</v>
       </c>
       <c r="D6" t="n">
-        <v>2.062613465602023</v>
+        <v>2.019833227690339</v>
       </c>
       <c r="E6" t="n">
-        <v>7.537198470806663</v>
+        <v>7.69943640483744</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469623303517336</v>
+        <v>0.7424497338934836</v>
       </c>
       <c r="G6" t="n">
-        <v>31.44380973425161</v>
+        <v>30.91977663641358</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36026719617975</v>
+        <v>34.15268775910023</v>
       </c>
       <c r="I6" t="n">
-        <v>3.834027460953413</v>
+        <v>4.765035902198725</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668514564698336</v>
+        <v>4.640310836834272</v>
       </c>
       <c r="K6" t="n">
-        <v>15.34660677715647</v>
+        <v>15.06046949903192</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79819694184001</v>
+        <v>43.47673422946293</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87239173436261</v>
+        <v>99.84146193164999</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.0317351190819</v>
+        <v>82.86970274881327</v>
       </c>
       <c r="C7" t="n">
-        <v>40.70142971127173</v>
+        <v>39.97347879265207</v>
       </c>
       <c r="D7" t="n">
-        <v>1.983662718302596</v>
+        <v>1.920025815228961</v>
       </c>
       <c r="E7" t="n">
-        <v>7.781884497862025</v>
+        <v>7.981848140838008</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479216530306027</v>
+        <v>0.7436374952040884</v>
       </c>
       <c r="G7" t="n">
-        <v>30.24023363147678</v>
+        <v>29.39191638653887</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40439603940772</v>
+        <v>34.20732477938805</v>
       </c>
       <c r="I7" t="n">
-        <v>3.199126247560918</v>
+        <v>3.977215786589735</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674510331441267</v>
+        <v>4.647734345025552</v>
       </c>
       <c r="K7" t="n">
-        <v>16.96826488091808</v>
+        <v>17.13029725118674</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22380464500593</v>
+        <v>42.76386184776678</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89349923719574</v>
+        <v>99.8676378916056</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.8303948945545</v>
+        <v>80.57350065318448</v>
       </c>
       <c r="C8" t="n">
-        <v>43.00814398949969</v>
+        <v>38.29361682365194</v>
       </c>
       <c r="D8" t="n">
-        <v>1.987855895724429</v>
+        <v>1.81030791338669</v>
       </c>
       <c r="E8" t="n">
-        <v>9.613907001975456</v>
+        <v>8.078883163929667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495026517355999</v>
+        <v>0.7446585324650742</v>
       </c>
       <c r="G8" t="n">
-        <v>30.74779146507987</v>
+        <v>27.71234553312825</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4771219798376</v>
+        <v>34.2542924933934</v>
       </c>
       <c r="I8" t="n">
-        <v>5.569824326854042</v>
+        <v>3.318897188974694</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6843915733475</v>
+        <v>4.654115827906713</v>
       </c>
       <c r="K8" t="n">
-        <v>12.16960510544549</v>
+        <v>19.42649934681551</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63698172653205</v>
+        <v>42.16940561323839</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81473082147723</v>
+        <v>99.88952178370585</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.72016144090372</v>
+        <v>78.28758044133737</v>
       </c>
       <c r="C9" t="n">
-        <v>41.76241027292761</v>
+        <v>36.5212328739757</v>
       </c>
       <c r="D9" t="n">
-        <v>1.892218428832468</v>
+        <v>1.702257965012508</v>
       </c>
       <c r="E9" t="n">
-        <v>9.926359111483555</v>
+        <v>8.058188751669965</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508578840917165</v>
+        <v>0.7455364774956801</v>
       </c>
       <c r="G9" t="n">
-        <v>29.26848861693713</v>
+        <v>26.05830785144995</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53946266821896</v>
+        <v>34.29467796480127</v>
       </c>
       <c r="I9" t="n">
-        <v>4.649912955766655</v>
+        <v>2.769008446559989</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692861775573228</v>
+        <v>4.659602984348</v>
       </c>
       <c r="K9" t="n">
-        <v>14.2798385590963</v>
+        <v>21.71241955866265</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80303382556346</v>
+        <v>41.67415597877903</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84528265758736</v>
+        <v>99.90780841141736</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.30115365053017</v>
+        <v>84.15944188711545</v>
       </c>
       <c r="C10" t="n">
-        <v>40.06473749482782</v>
+        <v>40.62623812447497</v>
       </c>
       <c r="D10" t="n">
-        <v>1.783579321170869</v>
+        <v>1.704068179505619</v>
       </c>
       <c r="E10" t="n">
-        <v>10.00327510272557</v>
+        <v>10.32363330523866</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520239496773818</v>
+        <v>0.7463292956022448</v>
       </c>
       <c r="G10" t="n">
-        <v>27.58807876705016</v>
+        <v>27.89541008223576</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59310168515956</v>
+        <v>36.14053891304134</v>
       </c>
       <c r="I10" t="n">
-        <v>3.880945139263011</v>
+        <v>2.684904013977802</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700149685483637</v>
+        <v>4.66455809751403</v>
       </c>
       <c r="K10" t="n">
-        <v>16.69884634946983</v>
+        <v>15.84055811288454</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10725190693107</v>
+        <v>43.44380203372584</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87083575122873</v>
+        <v>99.91059827108535</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.71913607238992</v>
+        <v>83.45465502771371</v>
       </c>
       <c r="C11" t="n">
-        <v>38.08395972071466</v>
+        <v>40.20050972226551</v>
       </c>
       <c r="D11" t="n">
-        <v>1.668849643919497</v>
+        <v>1.664704083577802</v>
       </c>
       <c r="E11" t="n">
-        <v>9.899550180789358</v>
+        <v>10.52364568584153</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530296546026987</v>
+        <v>0.7470216268137232</v>
       </c>
       <c r="G11" t="n">
-        <v>25.81346110056407</v>
+        <v>27.30243026641596</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63936411172413</v>
+        <v>36.22547076534123</v>
       </c>
       <c r="I11" t="n">
-        <v>3.238446039523282</v>
+        <v>2.3224974321377</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706435341266867</v>
+        <v>4.668885167585771</v>
       </c>
       <c r="K11" t="n">
-        <v>19.28086392761012</v>
+        <v>16.54534497228628</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52737232002904</v>
+        <v>43.17680047319042</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8921959683538</v>
+        <v>99.92265516774221</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.05830135277893</v>
+        <v>81.11875326256815</v>
       </c>
       <c r="C12" t="n">
-        <v>35.92384003242066</v>
+        <v>38.22446898530036</v>
       </c>
       <c r="D12" t="n">
-        <v>1.551849600568616</v>
+        <v>1.567482524592363</v>
       </c>
       <c r="E12" t="n">
-        <v>9.655813659837067</v>
+        <v>10.23187265263738</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538984708431785</v>
+        <v>0.7476162066564946</v>
       </c>
       <c r="G12" t="n">
-        <v>24.00372582644494</v>
+        <v>25.70792175239384</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67932965878621</v>
+        <v>36.25430384585571</v>
       </c>
       <c r="I12" t="n">
-        <v>2.701818693529045</v>
+        <v>1.936954988829269</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711865442769867</v>
+        <v>4.672601291603092</v>
       </c>
       <c r="K12" t="n">
-        <v>21.94169864722109</v>
+        <v>18.88124673743185</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04450448592707</v>
+        <v>42.82977045970841</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91004316556881</v>
+        <v>99.93548618244063</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.43568952662267</v>
+        <v>82.44169756394889</v>
       </c>
       <c r="C13" t="n">
-        <v>33.71792832786105</v>
+        <v>39.31159075328537</v>
       </c>
       <c r="D13" t="n">
-        <v>1.43769521891181</v>
+        <v>1.568600667388383</v>
       </c>
       <c r="E13" t="n">
-        <v>9.321156289285922</v>
+        <v>10.91491884108711</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754649266914641</v>
+        <v>0.7481495087268817</v>
       </c>
       <c r="G13" t="n">
-        <v>22.23800672700818</v>
+        <v>26.10796413611695</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71386627807348</v>
+        <v>36.66186935087482</v>
       </c>
       <c r="I13" t="n">
-        <v>2.253757828212136</v>
+        <v>1.764260630211735</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716557918216507</v>
+        <v>4.675934429543011</v>
       </c>
       <c r="K13" t="n">
-        <v>24.56431047337731</v>
+        <v>17.5583024360511</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64271067949694</v>
+        <v>43.071340043481</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92494948073532</v>
+        <v>99.94123323281747</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.79682516100608</v>
+        <v>80.13089908760091</v>
       </c>
       <c r="C14" t="n">
-        <v>38.33732101259834</v>
+        <v>37.27387087561188</v>
       </c>
       <c r="D14" t="n">
-        <v>1.43936421662596</v>
+        <v>1.475577728765574</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86783944977774</v>
+        <v>10.51281607720439</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555253273514412</v>
+        <v>0.7486073493382933</v>
       </c>
       <c r="G14" t="n">
-        <v>24.31909721041301</v>
+        <v>24.55967998968468</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80943979014731</v>
+        <v>36.68430509731762</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88352587074413</v>
+        <v>1.471116911926023</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722033295946508</v>
+        <v>4.678795933364333</v>
       </c>
       <c r="K14" t="n">
-        <v>17.2031748389939</v>
+        <v>19.86910091239907</v>
       </c>
       <c r="L14" t="n">
-        <v>44.36349807132428</v>
+        <v>42.80802097226095</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90399392291653</v>
+        <v>99.9509927602719</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.84771075044847</v>
+        <v>79.1153498098969</v>
       </c>
       <c r="C15" t="n">
-        <v>37.83320149788052</v>
+        <v>36.448408501823</v>
       </c>
       <c r="D15" t="n">
-        <v>1.404431006234455</v>
+        <v>1.433601589056512</v>
       </c>
       <c r="E15" t="n">
-        <v>11.98069031460728</v>
+        <v>10.42416396706908</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562654250613355</v>
+        <v>0.7490055362439058</v>
       </c>
       <c r="G15" t="n">
-        <v>23.72887541000292</v>
+        <v>23.86102444727602</v>
       </c>
       <c r="H15" t="n">
-        <v>36.84549759139493</v>
+        <v>36.70381760937639</v>
       </c>
       <c r="I15" t="n">
-        <v>2.405292096514196</v>
+        <v>1.262452059350586</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726658906633348</v>
+        <v>4.681284601524411</v>
       </c>
       <c r="K15" t="n">
-        <v>18.15228924955155</v>
+        <v>20.8846501901031</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93441131171392</v>
+        <v>42.62488194428705</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91990205914598</v>
+        <v>99.95794063621315</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.16458445726488</v>
+        <v>76.55522668657838</v>
       </c>
       <c r="C16" t="n">
-        <v>35.52120420946049</v>
+        <v>34.08301298012573</v>
       </c>
       <c r="D16" t="n">
-        <v>1.303999360707169</v>
+        <v>1.331458953444153</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4582949932264</v>
+        <v>9.856873948476807</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756904240385026</v>
+        <v>0.7493487949497448</v>
       </c>
       <c r="G16" t="n">
-        <v>22.03201027860129</v>
+        <v>22.16095104887828</v>
       </c>
       <c r="H16" t="n">
-        <v>36.87662088183026</v>
+        <v>36.72063845291131</v>
       </c>
       <c r="I16" t="n">
-        <v>2.006103200108315</v>
+        <v>1.052525519482192</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730651502406413</v>
+        <v>4.683429968435906</v>
       </c>
       <c r="K16" t="n">
-        <v>20.83541554273512</v>
+        <v>23.44477331342159</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57656657845678</v>
+        <v>42.43714559369295</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93318633065239</v>
+        <v>99.96493188724028</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.95861057705139</v>
+        <v>82.26257769530908</v>
       </c>
       <c r="C17" t="n">
-        <v>36.82393077149944</v>
+        <v>37.92321250877959</v>
       </c>
       <c r="D17" t="n">
-        <v>1.305068976388633</v>
+        <v>1.332040184362889</v>
       </c>
       <c r="E17" t="n">
-        <v>12.27059401359821</v>
+        <v>11.86407812352492</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757525097012167</v>
+        <v>0.7496759133242282</v>
       </c>
       <c r="G17" t="n">
-        <v>22.52094780192088</v>
+        <v>23.99397316790453</v>
       </c>
       <c r="H17" t="n">
-        <v>37.37773481317955</v>
+        <v>38.56001641224677</v>
       </c>
       <c r="I17" t="n">
-        <v>1.992208018625911</v>
+        <v>1.077319435669308</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734531856326044</v>
+        <v>4.685474458276428</v>
       </c>
       <c r="K17" t="n">
-        <v>19.04138942294859</v>
+        <v>17.73742230469093</v>
       </c>
       <c r="L17" t="n">
-        <v>44.06832729776161</v>
+        <v>44.30347020815519</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93364749220964</v>
+        <v>99.96410502162571</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.48293739125219</v>
+        <v>84.04065041490159</v>
       </c>
       <c r="C18" t="n">
-        <v>34.65515826126319</v>
+        <v>38.6665731541342</v>
       </c>
       <c r="D18" t="n">
-        <v>1.216418995104949</v>
+        <v>1.333129396538454</v>
       </c>
       <c r="E18" t="n">
-        <v>11.71397489671893</v>
+        <v>12.47324649642592</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580596124993745</v>
+        <v>0.7502889249601434</v>
       </c>
       <c r="G18" t="n">
-        <v>20.99115770097483</v>
+        <v>24.14152607774729</v>
       </c>
       <c r="H18" t="n">
-        <v>37.40410882799857</v>
+        <v>38.5915470221032</v>
       </c>
       <c r="I18" t="n">
-        <v>1.661344779834457</v>
+        <v>2.06160671612569</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737872578121092</v>
+        <v>4.689305781000898</v>
       </c>
       <c r="K18" t="n">
-        <v>21.51706260874777</v>
+        <v>15.9593495850984</v>
       </c>
       <c r="L18" t="n">
-        <v>43.77244001836052</v>
+        <v>45.30541318366275</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94466088837149</v>
+        <v>99.93133592289536</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.52044175948571</v>
+        <v>81.10204391664189</v>
       </c>
       <c r="C19" t="n">
-        <v>33.94278554092552</v>
+        <v>36.04591866354065</v>
       </c>
       <c r="D19" t="n">
-        <v>1.182399279231865</v>
+        <v>1.230763685308897</v>
       </c>
       <c r="E19" t="n">
-        <v>11.61806782363499</v>
+        <v>11.80201203323474</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585127615143851</v>
+        <v>0.750819084796464</v>
       </c>
       <c r="G19" t="n">
-        <v>20.40409582204336</v>
+        <v>22.28779417930422</v>
       </c>
       <c r="H19" t="n">
-        <v>37.42646806570663</v>
+        <v>38.6188161014831</v>
       </c>
       <c r="I19" t="n">
-        <v>1.390193247889566</v>
+        <v>1.719219552536557</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740704759464908</v>
+        <v>4.692619279977901</v>
       </c>
       <c r="K19" t="n">
-        <v>22.4795582405143</v>
+        <v>18.89795608335812</v>
       </c>
       <c r="L19" t="n">
-        <v>43.53134412783628</v>
+        <v>44.9988583998755</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9536879092761</v>
+        <v>99.94273314677427</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.84420733518594</v>
+        <v>78.00476735442176</v>
       </c>
       <c r="C20" t="n">
-        <v>31.47992365766505</v>
+        <v>33.21289291383209</v>
       </c>
       <c r="D20" t="n">
-        <v>1.087660984558522</v>
+        <v>1.123525312562414</v>
       </c>
       <c r="E20" t="n">
-        <v>10.88036643231399</v>
+        <v>11.01261095959511</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758904324389205</v>
+        <v>0.7512790330388087</v>
       </c>
       <c r="G20" t="n">
-        <v>18.76924262440975</v>
+        <v>20.34582367072746</v>
       </c>
       <c r="H20" t="n">
-        <v>37.44578852565631</v>
+        <v>38.64247380671062</v>
       </c>
       <c r="I20" t="n">
-        <v>1.159092416425632</v>
+        <v>1.433560615294801</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743152027432532</v>
+        <v>4.695493956492555</v>
       </c>
       <c r="K20" t="n">
-        <v>25.15579266481406</v>
+        <v>21.99523264557822</v>
       </c>
       <c r="L20" t="n">
-        <v>43.32566719841284</v>
+        <v>44.74411834190813</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96138352089196</v>
+        <v>99.95224390131844</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.12473210608701</v>
+        <v>75.04110665474967</v>
       </c>
       <c r="C21" t="n">
-        <v>35.42762393173053</v>
+        <v>30.46868391726485</v>
       </c>
       <c r="D21" t="n">
-        <v>1.088387081020915</v>
+        <v>1.021556728948253</v>
       </c>
       <c r="E21" t="n">
-        <v>12.99005928636666</v>
+        <v>10.21234297043511</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759410950767329</v>
+        <v>0.7516779165843449</v>
       </c>
       <c r="G21" t="n">
-        <v>20.61341724807757</v>
+        <v>18.49928332226309</v>
       </c>
       <c r="H21" t="n">
-        <v>39.30243116472703</v>
+        <v>38.66299061375894</v>
       </c>
       <c r="I21" t="n">
-        <v>1.624707932831712</v>
+        <v>1.195268124107783</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746318442295807</v>
+        <v>4.697986978652156</v>
       </c>
       <c r="K21" t="n">
-        <v>18.87526789391299</v>
+        <v>24.95889334525032</v>
       </c>
       <c r="L21" t="n">
-        <v>45.64298737301479</v>
+        <v>44.53260160928217</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9458791986583</v>
+        <v>99.96017887179735</v>
       </c>
     </row>
   </sheetData>
